--- a/Cross-Docking-Results-v0.1.xlsx
+++ b/Cross-Docking-Results-v0.1.xlsx
@@ -606,7 +606,7 @@
         <v>104</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>6.999999999999999e-05</v>
+        <v>7.8e-05</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>1e-06</v>
@@ -618,7 +618,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>5 -&gt; 1 -&gt; 3 -&gt; 4 -&gt; 7 -&gt; 2 -&gt; 0 -&gt; 6</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -658,10 +658,10 @@
         <v>152</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>5.1e-05</v>
+        <v>0.000123</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>7 -&gt; 0 -&gt; 3 -&gt; 1 -&gt; 4 -&gt; 5 -&gt; 2 -&gt; 6</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
@@ -710,10 +710,10 @@
         <v>180.95</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>4.5e-05</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>0 -&gt; 5 -&gt; 1 -&gt; 3 -&gt; 7 -&gt; 2 -&gt; 6 -&gt; 4</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
         <v>205.71</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>6.3e-05</v>
+        <v>6.4e-05</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>1e-06</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 0 -&gt; 2 -&gt; 4 -&gt; 6 -&gt; 1 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 11 -&gt; 3 -&gt; 8</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
@@ -814,7 +814,7 @@
         <v>117.95</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>6.1e-05</v>
+        <v>6.7e-05</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>1e-06</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 4 -&gt; 6 -&gt; 11 -&gt; 1 -&gt; 5 -&gt; 10 -&gt; 3 -&gt; 2 -&gt; 8 -&gt; 0 -&gt; 7</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
         <v>191.89</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>6.4e-05</v>
+        <v>5.9e-05</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>1e-06</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>3 -&gt; 8 -&gt; 7 -&gt; 1 -&gt; 5 -&gt; 11 -&gt; 9 -&gt; 2 -&gt; 4 -&gt; 10 -&gt; 6 -&gt; 0</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
@@ -887,7 +887,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_uniform_s103</t>
@@ -918,10 +918,10 @@
         <v>196.23</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>9.500000000000001e-05</v>
+        <v>8.4e-05</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>2e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 13 -&gt; 7 -&gt; 18 -&gt; 15 -&gt; 1 -&gt; 16 -&gt; 11 -&gt; 14 -&gt; 4 -&gt; 8 -&gt; 0 -&gt; 3 -&gt; 12 -&gt; 5 -&gt; 6 -&gt; 19 -&gt; 17 -&gt; 10 -&gt; 2</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_uniform_s113</t>
@@ -982,7 +982,7 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>13 -&gt; 6 -&gt; 0 -&gt; 15 -&gt; 17 -&gt; 10 -&gt; 5 -&gt; 19 -&gt; 16 -&gt; 9 -&gt; 11 -&gt; 7 -&gt; 8 -&gt; 18 -&gt; 1 -&gt; 4 -&gt; 3 -&gt; 14 -&gt; 2 -&gt; 12</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_uniform_s123</t>
@@ -1022,10 +1022,10 @@
         <v>266.67</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>8.7e-05</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>2e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>10 -&gt; 17 -&gt; 0 -&gt; 2 -&gt; 6 -&gt; 19 -&gt; 18 -&gt; 5 -&gt; 1 -&gt; 15 -&gt; 14 -&gt; 11 -&gt; 4 -&gt; 12 -&gt; 13 -&gt; 3 -&gt; 7 -&gt; 16 -&gt; 9 -&gt; 8</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
         <v>475</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>9.399999999999999e-05</v>
+        <v>9.3e-05</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>2e-06</v>
@@ -1126,10 +1126,10 @@
         <v>648.28</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.000163</v>
+        <v>0.000149</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>3e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>1095.65</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.000246</v>
+        <v>0.000237</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>4e-06</v>
@@ -1230,10 +1230,10 @@
         <v>702.27</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.001143</v>
+        <v>0.000327</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.9e-05</v>
+        <v>5e-06</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -1282,10 +1282,10 @@
         <v>840.91</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.000699</v>
+        <v>0.000465</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.2e-05</v>
+        <v>8e-06</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
         <v>1425.58</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.001572</v>
+        <v>0.001298</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2.6e-05</v>
+        <v>2.2e-05</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>2178.57</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.003013</v>
+        <v>0.003028</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>5e-05</v>
@@ -1541,7 +1541,7 @@
         <v>100</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>4.7e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>1e-06</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>5 -&gt; 1 -&gt; 3 -&gt; 4 -&gt; 7 -&gt; 2 -&gt; 0 -&gt; 6</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -1593,7 +1593,7 @@
         <v>148</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>4.2e-05</v>
+        <v>4.8e-05</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>1e-06</v>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>7 -&gt; 0 -&gt; 3 -&gt; 1 -&gt; 4 -&gt; 5 -&gt; 2 -&gt; 6</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
@@ -1645,7 +1645,7 @@
         <v>176.19</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>4.2e-05</v>
+        <v>4.7e-05</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>1e-06</v>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>0 -&gt; 5 -&gt; 1 -&gt; 3 -&gt; 7 -&gt; 2 -&gt; 6 -&gt; 4</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
         <v>200</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>5.5e-05</v>
+        <v>6.1e-05</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>1e-06</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 0 -&gt; 2 -&gt; 4 -&gt; 6 -&gt; 1 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 11 -&gt; 3 -&gt; 8</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
@@ -1749,7 +1749,7 @@
         <v>112.82</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>5.6e-05</v>
+        <v>5.9e-05</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>1e-06</v>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 4 -&gt; 6 -&gt; 11 -&gt; 1 -&gt; 5 -&gt; 10 -&gt; 3 -&gt; 2 -&gt; 8 -&gt; 0 -&gt; 7</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
         <v>189.19</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>5.1e-05</v>
+        <v>6.1e-05</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>1e-06</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>3 -&gt; 8 -&gt; 7 -&gt; 1 -&gt; 5 -&gt; 11 -&gt; 9 -&gt; 2 -&gt; 4 -&gt; 10 -&gt; 6 -&gt; 0</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_sparse_s103</t>
@@ -1853,10 +1853,10 @@
         <v>192.45</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.00022</v>
+        <v>9.3e-05</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>4e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 13 -&gt; 7 -&gt; 18 -&gt; 15 -&gt; 1 -&gt; 16 -&gt; 11 -&gt; 14 -&gt; 4 -&gt; 8 -&gt; 0 -&gt; 3 -&gt; 12 -&gt; 5 -&gt; 6 -&gt; 19 -&gt; 17 -&gt; 10 -&gt; 2</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_sparse_s113</t>
@@ -1905,7 +1905,7 @@
         <v>103.17</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>8.3e-05</v>
+        <v>8.4e-05</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>1e-06</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>13 -&gt; 6 -&gt; 0 -&gt; 15 -&gt; 17 -&gt; 10 -&gt; 5 -&gt; 19 -&gt; 16 -&gt; 9 -&gt; 11 -&gt; 7 -&gt; 8 -&gt; 18 -&gt; 1 -&gt; 4 -&gt; 3 -&gt; 14 -&gt; 2 -&gt; 12</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_sparse_s123</t>
@@ -1957,7 +1957,7 @@
         <v>264.29</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>7.8e-05</v>
+        <v>8.8e-05</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>1e-06</v>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>10 -&gt; 17 -&gt; 0 -&gt; 2 -&gt; 6 -&gt; 19 -&gt; 18 -&gt; 5 -&gt; 1 -&gt; 15 -&gt; 14 -&gt; 11 -&gt; 4 -&gt; 12 -&gt; 13 -&gt; 3 -&gt; 7 -&gt; 16 -&gt; 9 -&gt; 8</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2009,10 +2009,10 @@
         <v>460.71</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>8.4e-05</v>
+        <v>9.6e-05</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>644.83</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.000181</v>
+        <v>0.000154</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>3e-06</v>
@@ -2113,7 +2113,7 @@
         <v>1086.96</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.000232</v>
+        <v>0.000244</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>4e-06</v>
@@ -2165,10 +2165,10 @@
         <v>704.55</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.001077</v>
+        <v>0.000351</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.8e-05</v>
+        <v>6e-06</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -2217,10 +2217,10 @@
         <v>838.64</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.000733</v>
+        <v>0.000467</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.2e-05</v>
+        <v>8e-06</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
@@ -2269,10 +2269,10 @@
         <v>1418.6</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.001574</v>
+        <v>0.001606</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2.6e-05</v>
+        <v>2.7e-05</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
         <v>2176.19</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.003114</v>
+        <v>0.002894</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>5.2e-05</v>
+        <v>4.8e-05</v>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>100</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>4.4e-05</v>
+        <v>5.3e-05</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>1e-06</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>5 -&gt; 1 -&gt; 3 -&gt; 4 -&gt; 7 -&gt; 2 -&gt; 0 -&gt; 6</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
         <v>148</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>4e-05</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>1e-06</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>7 -&gt; 0 -&gt; 3 -&gt; 1 -&gt; 4 -&gt; 5 -&gt; 2 -&gt; 6</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
@@ -2580,7 +2580,7 @@
         <v>176.19</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>4.4e-05</v>
+        <v>5.1e-05</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>1e-06</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>0 -&gt; 5 -&gt; 1 -&gt; 3 -&gt; 7 -&gt; 2 -&gt; 6 -&gt; 4</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
         <v>200</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>5.7e-05</v>
+        <v>6.7e-05</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>1e-06</v>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 0 -&gt; 2 -&gt; 4 -&gt; 6 -&gt; 1 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 11 -&gt; 3 -&gt; 8</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
@@ -2684,7 +2684,7 @@
         <v>112.82</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>5.9e-05</v>
+        <v>6.4e-05</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>1e-06</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 4 -&gt; 6 -&gt; 11 -&gt; 1 -&gt; 5 -&gt; 10 -&gt; 3 -&gt; 2 -&gt; 8 -&gt; 0 -&gt; 7</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>3 -&gt; 8 -&gt; 7 -&gt; 1 -&gt; 5 -&gt; 11 -&gt; 9 -&gt; 2 -&gt; 4 -&gt; 10 -&gt; 6 -&gt; 0</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_clustered_s103</t>
@@ -2788,7 +2788,7 @@
         <v>192.45</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>8.4e-05</v>
+        <v>8.8e-05</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>1e-06</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 13 -&gt; 7 -&gt; 18 -&gt; 15 -&gt; 1 -&gt; 16 -&gt; 11 -&gt; 14 -&gt; 4 -&gt; 8 -&gt; 0 -&gt; 3 -&gt; 12 -&gt; 5 -&gt; 6 -&gt; 19 -&gt; 17 -&gt; 10 -&gt; 2</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_clustered_s113</t>
@@ -2840,7 +2840,7 @@
         <v>103.17</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>8.000000000000001e-05</v>
+        <v>8.6e-05</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>1e-06</v>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>13 -&gt; 6 -&gt; 0 -&gt; 15 -&gt; 17 -&gt; 10 -&gt; 5 -&gt; 19 -&gt; 16 -&gt; 9 -&gt; 11 -&gt; 7 -&gt; 8 -&gt; 18 -&gt; 1 -&gt; 4 -&gt; 3 -&gt; 14 -&gt; 2 -&gt; 12</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_clustered_s123</t>
@@ -2892,10 +2892,10 @@
         <v>264.29</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>8.899999999999999e-05</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>10 -&gt; 17 -&gt; 0 -&gt; 2 -&gt; 6 -&gt; 19 -&gt; 18 -&gt; 5 -&gt; 1 -&gt; 15 -&gt; 14 -&gt; 11 -&gt; 4 -&gt; 12 -&gt; 13 -&gt; 3 -&gt; 7 -&gt; 16 -&gt; 9 -&gt; 8</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2944,10 +2944,10 @@
         <v>457.14</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>8.3e-05</v>
+        <v>0.000103</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>651.72</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.000153</v>
+        <v>0.000156</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>3e-06</v>
@@ -3048,10 +3048,10 @@
         <v>1091.3</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.000241</v>
+        <v>0.000277</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>4e-06</v>
+        <v>5e-06</v>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
@@ -3100,10 +3100,10 @@
         <v>697.73</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.001153</v>
+        <v>0.000391</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.9e-05</v>
+        <v>7e-06</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -3152,10 +3152,10 @@
         <v>840.91</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.000657</v>
+        <v>0.000528</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.1e-05</v>
+        <v>9e-06</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
@@ -3204,10 +3204,10 @@
         <v>1418.6</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.001711</v>
+        <v>0.001377</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2.9e-05</v>
+        <v>2.3e-05</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -3256,10 +3256,10 @@
         <v>2178.57</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.00304</v>
+        <v>0.003021</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>5.1e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>4.1e-05</v>
+        <v>6.8e-05</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>1e-06</v>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>5 -&gt; 1 -&gt; 3 -&gt; 4 -&gt; 7 -&gt; 2 -&gt; 0 -&gt; 6</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -3463,7 +3463,7 @@
         <v>130</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>4.1e-05</v>
+        <v>5.7e-05</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>1e-06</v>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>7 -&gt; 3 -&gt; 0 -&gt; 1 -&gt; 4 -&gt; 5 -&gt; 2 -&gt; 6</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
@@ -3515,7 +3515,7 @@
         <v>151.02</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>4.7e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>1e-06</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>0 -&gt; 5 -&gt; 1 -&gt; 3 -&gt; 7 -&gt; 2 -&gt; 6 -&gt; 4</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3567,10 +3567,10 @@
         <v>85.09</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>5.7e-05</v>
+        <v>0.000176</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>1e-06</v>
+        <v>3e-06</v>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 0 -&gt; 2 -&gt; 4 -&gt; 6 -&gt; 1 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 11 -&gt; 3 -&gt; 8</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
@@ -3619,7 +3619,7 @@
         <v>116.19</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>5.5e-05</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>1e-06</v>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 4 -&gt; 6 -&gt; 11 -&gt; 1 -&gt; 5 -&gt; 10 -&gt; 3 -&gt; 2 -&gt; 8 -&gt; 0 -&gt; 7</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
         <v>103.88</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>5.1e-05</v>
+        <v>6.9e-05</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>1e-06</v>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>3 -&gt; 8 -&gt; 7 -&gt; 1 -&gt; 5 -&gt; 11 -&gt; 2 -&gt; 9 -&gt; 4 -&gt; 10 -&gt; 6 -&gt; 0</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
@@ -3692,7 +3692,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_asymmetric_s103</t>
@@ -3723,10 +3723,10 @@
         <v>163.03</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>8.2e-05</v>
+        <v>0.000103</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 13 -&gt; 7 -&gt; 18 -&gt; 15 -&gt; 1 -&gt; 16 -&gt; 11 -&gt; 14 -&gt; 8 -&gt; 4 -&gt; 0 -&gt; 3 -&gt; 5 -&gt; 12 -&gt; 6 -&gt; 19 -&gt; 17 -&gt; 10 -&gt; 2</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_asymmetric_s113</t>
@@ -3775,10 +3775,10 @@
         <v>85.81999999999999</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>8.1e-05</v>
+        <v>9.3e-05</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>6 -&gt; 0 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 10 -&gt; 5 -&gt; 16 -&gt; 19 -&gt; 9 -&gt; 11 -&gt; 7 -&gt; 8 -&gt; 18 -&gt; 1 -&gt; 4 -&gt; 3 -&gt; 14 -&gt; 2 -&gt; 12</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
@@ -3796,7 +3796,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_asymmetric_s123</t>
@@ -3827,7 +3827,7 @@
         <v>88.15000000000001</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.000101</v>
+        <v>9.899999999999999e-05</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>2e-06</v>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>10 -&gt; 0 -&gt; 17 -&gt; 2 -&gt; 6 -&gt; 19 -&gt; 18 -&gt; 5 -&gt; 1 -&gt; 15 -&gt; 14 -&gt; 11 -&gt; 4 -&gt; 12 -&gt; 13 -&gt; 3 -&gt; 7 -&gt; 16 -&gt; 9 -&gt; 8</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
         <v>114.44</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>9.399999999999999e-05</v>
+        <v>9.8e-05</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>2e-06</v>
@@ -3931,7 +3931,7 @@
         <v>230.26</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.000159</v>
+        <v>0.000161</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>3e-06</v>
@@ -3983,7 +3983,7 @@
         <v>298.68</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.000246</v>
+        <v>0.000239</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>4e-06</v>
@@ -4035,10 +4035,10 @@
         <v>214.73</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.000552</v>
+        <v>0.000385</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>9e-06</v>
+        <v>6e-06</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -4087,10 +4087,10 @@
         <v>269.6</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.000802</v>
+        <v>0.000491</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.3e-05</v>
+        <v>8e-06</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
@@ -4139,10 +4139,10 @@
         <v>506.84</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.001773</v>
+        <v>0.001326</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>3e-05</v>
+        <v>2.2e-05</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -4191,10 +4191,10 @@
         <v>803.54</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.003205</v>
+        <v>0.002919</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>5.3e-05</v>
+        <v>4.9e-05</v>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>97.56</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>5e-05</v>
+        <v>5.8e-05</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>1e-06</v>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>5 -&gt; 1 -&gt; 3 -&gt; 4 -&gt; 0 -&gt; 2 -&gt; 7 -&gt; 6</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
         <v>128.89</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>6.7e-05</v>
+        <v>5.9e-05</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>1e-06</v>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>7 -&gt; 3 -&gt; 0 -&gt; 1 -&gt; 5 -&gt; 4 -&gt; 2 -&gt; 6</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
@@ -4450,7 +4450,7 @@
         <v>132.5</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>4.9e-05</v>
+        <v>4.8e-05</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>1e-06</v>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>0 -&gt; 1 -&gt; 5 -&gt; 3 -&gt; 6 -&gt; 2 -&gt; 7 -&gt; 4</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>cd_n0012_m0008_congested_s102</t>
@@ -4502,7 +4502,7 @@
         <v>111.27</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>6.8e-05</v>
+        <v>6.7e-05</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>1e-06</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>4 -&gt; 9 -&gt; 0 -&gt; 11 -&gt; 3 -&gt; 10 -&gt; 5 -&gt; 8 -&gt; 2 -&gt; 1 -&gt; 6 -&gt; 7</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
@@ -4523,7 +4523,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>cd_n0012_m0008_congested_s112</t>
@@ -4554,7 +4554,7 @@
         <v>167.21</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>6.3e-05</v>
+        <v>6.7e-05</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>1e-06</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>11 -&gt; 9 -&gt; 10 -&gt; 4 -&gt; 6 -&gt; 7 -&gt; 0 -&gt; 2 -&gt; 3 -&gt; 5 -&gt; 8 -&gt; 1</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>cd_n0012_m0008_congested_s122</t>
@@ -4606,7 +4606,7 @@
         <v>161.02</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>5.9e-05</v>
+        <v>6.3e-05</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>1e-06</v>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>4 -&gt; 1 -&gt; 7 -&gt; 6 -&gt; 3 -&gt; 8 -&gt; 0 -&gt; 2 -&gt; 11 -&gt; 9 -&gt; 10 -&gt; 5</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_congested_s103</t>
@@ -4658,10 +4658,10 @@
         <v>137.86</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>8.6e-05</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>10 -&gt; 7 -&gt; 18 -&gt; 16 -&gt; 5 -&gt; 19 -&gt; 14 -&gt; 1 -&gt; 12 -&gt; 17 -&gt; 13 -&gt; 8 -&gt; 2 -&gt; 3 -&gt; 6 -&gt; 0 -&gt; 4 -&gt; 15 -&gt; 9 -&gt; 11</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_congested_s113</t>
@@ -4710,10 +4710,10 @@
         <v>121.7</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>8.7e-05</v>
+        <v>9.1e-05</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>11 -&gt; 0 -&gt; 4 -&gt; 10 -&gt; 13 -&gt; 8 -&gt; 18 -&gt; 3 -&gt; 15 -&gt; 17 -&gt; 7 -&gt; 12 -&gt; 9 -&gt; 5 -&gt; 19 -&gt; 16 -&gt; 6 -&gt; 14 -&gt; 2 -&gt; 1</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_congested_s123</t>
@@ -4762,10 +4762,10 @@
         <v>176.74</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>8.4e-05</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>6 -&gt; 12 -&gt; 0 -&gt; 2 -&gt; 5 -&gt; 14 -&gt; 19 -&gt; 13 -&gt; 1 -&gt; 11 -&gt; 10 -&gt; 15 -&gt; 17 -&gt; 4 -&gt; 7 -&gt; 3 -&gt; 16 -&gt; 8 -&gt; 9 -&gt; 18</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
         <v>125.49</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.0001</v>
+        <v>9.2e-05</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>2e-06</v>
@@ -4866,7 +4866,7 @@
         <v>131.37</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.000164</v>
+        <v>0.00017</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>3e-06</v>
@@ -4970,10 +4970,10 @@
         <v>115.38</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.001103</v>
+        <v>0.000361</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.8e-05</v>
+        <v>6e-06</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -5022,10 +5022,10 @@
         <v>120.51</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.000714</v>
+        <v>0.0005330000000000001</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.2e-05</v>
+        <v>9e-06</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
@@ -5074,10 +5074,10 @@
         <v>126.92</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.001572</v>
+        <v>0.001291</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2.6e-05</v>
+        <v>2.2e-05</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -5126,10 +5126,10 @@
         <v>129.87</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.00304</v>
+        <v>0.002868</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>5.1e-05</v>
+        <v>4.8e-05</v>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>133.33</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>5.6e-05</v>
+        <v>5.3e-05</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>1e-06</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>0 -&gt; 5 -&gt; 4 -&gt; 1 -&gt; 7 -&gt; 2 -&gt; 6 -&gt; 3</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
         <v>137.04</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>5.5e-05</v>
+        <v>5.2e-05</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>1e-06</v>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>0 -&gt; 7 -&gt; 2 -&gt; 3 -&gt; 5 -&gt; 6 -&gt; 4 -&gt; 1</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
@@ -5385,7 +5385,7 @@
         <v>96.67</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>4.9e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>1e-06</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>3 -&gt; 5 -&gt; 4 -&gt; 1 -&gt; 2 -&gt; 6 -&gt; 7 -&gt; 0</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5406,7 +5406,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>cd_n0012_m0008_urgent_s102</t>
@@ -5437,7 +5437,7 @@
         <v>129.17</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>6.600000000000001e-05</v>
+        <v>5.8e-05</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>1e-06</v>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>8 -&gt; 0 -&gt; 11 -&gt; 9 -&gt; 5 -&gt; 3 -&gt; 4 -&gt; 6 -&gt; 1 -&gt; 7 -&gt; 2 -&gt; 10</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
@@ -5489,7 +5489,7 @@
         <v>117.02</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>5.8e-05</v>
+        <v>6.600000000000001e-05</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>1e-06</v>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>2 -&gt; 7 -&gt; 11 -&gt; 4 -&gt; 9 -&gt; 8 -&gt; 10 -&gt; 5 -&gt; 6 -&gt; 1 -&gt; 3 -&gt; 0</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5541,7 +5541,7 @@
         <v>131.91</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>6e-05</v>
+        <v>6.4e-05</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>1e-06</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 8 -&gt; 4 -&gt; 3 -&gt; 1 -&gt; 2 -&gt; 11 -&gt; 10 -&gt; 0 -&gt; 5 -&gt; 6 -&gt; 7</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
@@ -5562,7 +5562,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_urgent_s103</t>
@@ -5593,7 +5593,7 @@
         <v>151.56</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>9.3e-05</v>
+        <v>9.2e-05</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>2e-06</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>14 -&gt; 5 -&gt; 18 -&gt; 13 -&gt; 17 -&gt; 3 -&gt; 2 -&gt; 4 -&gt; 19 -&gt; 0 -&gt; 12 -&gt; 15 -&gt; 6 -&gt; 8 -&gt; 7 -&gt; 9 -&gt; 1 -&gt; 10 -&gt; 11 -&gt; 16</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_urgent_s113</t>
@@ -5645,10 +5645,10 @@
         <v>166.1</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>8.500000000000001e-05</v>
+        <v>9.3e-05</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>8 -&gt; 15 -&gt; 12 -&gt; 6 -&gt; 19 -&gt; 9 -&gt; 2 -&gt; 5 -&gt; 17 -&gt; 14 -&gt; 0 -&gt; 16 -&gt; 3 -&gt; 18 -&gt; 11 -&gt; 4 -&gt; 1 -&gt; 7 -&gt; 10 -&gt; 13</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
@@ -5666,7 +5666,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_urgent_s123</t>
@@ -5697,10 +5697,10 @@
         <v>106.02</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>8.7e-05</v>
+        <v>0.000102</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>19 -&gt; 1 -&gt; 16 -&gt; 17 -&gt; 13 -&gt; 10 -&gt; 9 -&gt; 18 -&gt; 14 -&gt; 3 -&gt; 0 -&gt; 2 -&gt; 7 -&gt; 12 -&gt; 8 -&gt; 15 -&gt; 11 -&gt; 4 -&gt; 6 -&gt; 5</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
         <v>196.67</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.000106</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>2e-06</v>
@@ -5801,7 +5801,7 @@
         <v>237.5</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.00019</v>
+        <v>0.000169</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>3e-06</v>
@@ -5853,7 +5853,7 @@
         <v>261.76</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.00026</v>
+        <v>0.000249</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>4e-06</v>
@@ -5905,10 +5905,10 @@
         <v>200</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.001144</v>
+        <v>0.000363</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.9e-05</v>
+        <v>6e-06</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -5957,10 +5957,10 @@
         <v>258</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.00081</v>
+        <v>0.000501</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.3e-05</v>
+        <v>8e-06</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>365.45</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.00169</v>
+        <v>0.001391</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2.8e-05</v>
+        <v>2.3e-05</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -6061,10 +6061,10 @@
         <v>607.6900000000001</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.003199</v>
+        <v>0.002927</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>5.3e-05</v>
+        <v>4.9e-05</v>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>171.43</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>5.9e-05</v>
+        <v>5.1e-05</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>1e-06</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>5 -&gt; 1 -&gt; 3 -&gt; 4 -&gt; 7 -&gt; 2 -&gt; 0 -&gt; 6</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
         <v>91.38</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>6.499999999999999e-05</v>
+        <v>5.2e-05</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>1e-06</v>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>7 -&gt; 3 -&gt; 0 -&gt; 1 -&gt; 4 -&gt; 5 -&gt; 2 -&gt; 6</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
@@ -6320,7 +6320,7 @@
         <v>125</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>5.8e-05</v>
+        <v>4.7e-05</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>1e-06</v>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>0 -&gt; 5 -&gt; 1 -&gt; 3 -&gt; 7 -&gt; 2 -&gt; 6 -&gt; 4</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
         <v>89.77</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>6.1e-05</v>
+        <v>6.4e-05</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>1e-06</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 0 -&gt; 2 -&gt; 4 -&gt; 6 -&gt; 1 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 11 -&gt; 3 -&gt; 8</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
@@ -6424,7 +6424,7 @@
         <v>120.55</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>6.4e-05</v>
+        <v>6.7e-05</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>1e-06</v>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 4 -&gt; 6 -&gt; 11 -&gt; 1 -&gt; 5 -&gt; 10 -&gt; 3 -&gt; 8 -&gt; 2 -&gt; 0 -&gt; 7</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
         <v>81.01000000000001</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>6.1e-05</v>
+        <v>6.3e-05</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>1e-06</v>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>3 -&gt; 8 -&gt; 7 -&gt; 1 -&gt; 5 -&gt; 11 -&gt; 2 -&gt; 9 -&gt; 4 -&gt; 10 -&gt; 6 -&gt; 0</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
@@ -6497,7 +6497,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_mixed_s103</t>
@@ -6528,7 +6528,7 @@
         <v>187.36</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>9.3e-05</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>2e-06</v>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>9 -&gt; 13 -&gt; 7 -&gt; 18 -&gt; 15 -&gt; 1 -&gt; 16 -&gt; 11 -&gt; 14 -&gt; 4 -&gt; 8 -&gt; 0 -&gt; 3 -&gt; 5 -&gt; 12 -&gt; 6 -&gt; 19 -&gt; 17 -&gt; 10 -&gt; 2</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_mixed_s113</t>
@@ -6580,10 +6580,10 @@
         <v>125</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>8.4e-05</v>
+        <v>9.6e-05</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>0 -&gt; 13 -&gt; 6 -&gt; 15 -&gt; 17 -&gt; 10 -&gt; 5 -&gt; 16 -&gt; 19 -&gt; 9 -&gt; 11 -&gt; 7 -&gt; 8 -&gt; 18 -&gt; 1 -&gt; 4 -&gt; 3 -&gt; 14 -&gt; 2 -&gt; 12</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
@@ -6601,7 +6601,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>cd_n0020_m0013_mixed_s123</t>
@@ -6632,10 +6632,10 @@
         <v>135.29</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>8.7e-05</v>
+        <v>9.7e-05</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>(n&lt;=20: not found)</t>
+          <t>10 -&gt; 17 -&gt; 0 -&gt; 2 -&gt; 6 -&gt; 19 -&gt; 18 -&gt; 5 -&gt; 1 -&gt; 15 -&gt; 14 -&gt; 11 -&gt; 4 -&gt; 12 -&gt; 13 -&gt; 3 -&gt; 7 -&gt; 16 -&gt; 9 -&gt; 8</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6736,7 +6736,7 @@
         <v>402.13</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.000168</v>
+        <v>0.000171</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>3e-06</v>
@@ -6788,10 +6788,10 @@
         <v>625.58</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.000268</v>
+        <v>0.000281</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>4e-06</v>
+        <v>5e-06</v>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
@@ -6840,10 +6840,10 @@
         <v>385</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.001163</v>
+        <v>0.000388</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.9e-05</v>
+        <v>6e-06</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -6892,10 +6892,10 @@
         <v>535.71</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.000693</v>
+        <v>0.000536</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.2e-05</v>
+        <v>9e-06</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
@@ -6944,10 +6944,10 @@
         <v>809.33</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.001489</v>
+        <v>0.001417</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2.5e-05</v>
+        <v>2.4e-05</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         <v>1254.79</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.003015</v>
+        <v>0.002959</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>5e-05</v>
+        <v>4.9e-05</v>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
